--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92174</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92190</v>
+        <v>92193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92193</v>
+        <v>92195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92195</v>
+        <v>92199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92199</v>
+        <v>92200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92231</v>
+        <v>92237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92237</v>
+        <v>92238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129344439</v>
       </c>
       <c r="B3" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 62402-2022 artfynd.xlsx
+++ b/artfynd/A 62402-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129344458</v>
       </c>
       <c r="B2" t="n">
-        <v>92243</v>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129344439</v>
+        <v>129344443</v>
       </c>
       <c r="B3" t="n">
-        <v>92913</v>
+        <v>87322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690203</v>
+        <v>690149</v>
       </c>
       <c r="R3" t="n">
-        <v>6617273</v>
+        <v>6617534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +866,394 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129344462</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brännmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>690163</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6617542</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129344437</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brännmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>690154</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6617319</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129344439</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brännmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>690203</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6617273</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129344457</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brännmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>690163</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6617534</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
